--- a/public/documents/pieces-reponse-1/R1-sur-versement-fourchette.xlsx
+++ b/public/documents/pieces-reponse-1/R1-sur-versement-fourchette.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Regimes de service" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fourchette par boisson" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sources et conventions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fourchette 3 exercices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lignes plafonnees" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sources et conventions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15126,6 +15128,4103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fourchette de sur-versement compatible avec le stock, par boisson, sur les trois exercices cumules</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le taux n'est pas postule : il est encadre. La borne basse est 0 %, la borne haute est ce que le bilan matiere autorise (ecart / base versee a la main). Le taux retenu est le PLUS PETIT des deux : celui de la mesure publiee, ou celui du plafond de stock. Une boisson sans achat facture connu n'est bornee par rien : elle est signalee comme telle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Boisson</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Categorie</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Achats factures (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Disponible au service (L)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Vendu aux doses de la carte (L)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>dont verre (L)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>dont pichet (L)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>dont bouteille (L)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>dont cocktails (L)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Ecart (L)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Base versee a la main (L)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Borne basse</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Borne haute compatible avec le stock</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Taux des sources</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement aux taux des sources (L)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement plafonne par le stock (L)</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Taux effectif rapporte au volume vendu</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Macvin</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>vin_de_liqueur</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>806.2</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>686.79</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>227.78</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>339.17</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>293.27</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>115,7 %</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>37,9 %</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>32,0 %</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>516</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>512.25</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>429.47</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>231.59</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>82.78</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>231.59</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>35,7 %</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>10,1 %</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Bourgogne Aligoté maison</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>137.59</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>303.16</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>189.34</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>160,1 %</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>37,0 %</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>20,2 %</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>vin_rouge</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>462.7</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>464.2</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>346.08</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>118.12</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>130.2</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>90,7 %</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>8,9 %</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Saint Véran</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>465</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>478.5</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>245.43</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>122.93</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>233.07</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>122.93</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>189,6 %</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>11,8 %</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>vin_rose</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>681</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>681</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>286.75</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>224.25</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>630,8 %</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>25,5 %</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>5,6 %</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune rouge</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>vin_rouge</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>39,8 %</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>7,8 %</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Moulin à Vent</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>vin_rouge</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>171,6 %</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>12,8 %</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Saint Joseph Rouge</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>vin_rouge</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>165.15</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>136,4 %</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>7,7 %</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>131.3</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>129,1 %</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>30,7 %</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Cubis de vin (couleur non précisée)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>vin</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>426.89</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>378.29</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-426.89</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>2,7 %</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Macon</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>139.82</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>97,7 %</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>8,1 %</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Gewurztraminer</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>78.88</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-67.63</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>12,9 %</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>conso superieure aux achats factures : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Vin Jaune</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>vin</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>154,4 %</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>18,2 %</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>vin_rouge</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>190.78</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>157.25</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>169.22</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>504,7 %</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>4,2 %</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Chardonnay</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>203.2</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>170.57</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>522,7 %</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Picon</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>aperitif</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>157,9 %</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>28,9 %</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>vin</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>37,3 %</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>23,5 %</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Soho Litchi</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>122,2 %</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>vin_blanc</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>-62.45</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>7,1 %</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>conso superieure aux achats factures : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Liqueur de Cerise</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>conso superieure aux achats factures : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Martini Blanc</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>aperitif</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>20,1 %</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>20,0 %</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>conso superieure aux achats factures : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Vodka</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>spiritueux</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>202,3 %</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Passoa</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>52,2 %</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>42,1 %</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>30,2 %</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>aperitif</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>486,4 %</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>20,0 %</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>8,4 %</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Pontarlier Anis</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>aperitif</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>357,8 %</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>23,3 %</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>23,3 %</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Clan Campbell</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>spiritueux</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>67,2 %</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>30,6 %</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>21,5 %</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ricard</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>aperitif</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>73,1 %</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>20,0 %</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>20,0 %</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Pastis 51</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>aperitif</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>15,7 %</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>20,1 %</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>20,1 %</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>plafonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Get 27</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>261,4 %</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>19,9 %</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>19,9 %</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Sapin</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>474,1 %</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27,2 %</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>27,2 %</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Jack Daniel's</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>spiritueux</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>87,9 %</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>20,1 %</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>20,1 %</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>20,0 %</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P37" s="10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>15,0 %</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Génépi</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>322,4 %</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>20,3 %</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>20,3 %</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>20,3 %</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P39" s="10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>20,3 %</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>-32.54</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>-46.51</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>20,1 %</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P40" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>2,1 %</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>conso superieure aux achats factures : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>887,5 %</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>19,9 %</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>5,0 %</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Bailey's</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>386,4 %</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>19,7 %</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>1,7 %</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Tequila Camino Real</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>spiritueux</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>175,6 %</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>40,9 %</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>40,9 %</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Mirabelle</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>337,5 %</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>19,6 %</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>19,6 %</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Cognac</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>280,4 %</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>20,6 %</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>20,7 %</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Get 31</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>20,6 %</t>
+        </is>
+      </c>
+      <c r="O46" s="10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P46" s="10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>20,7 %</t>
+        </is>
+      </c>
+      <c r="R46" s="10" t="inlineStr">
+        <is>
+          <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Eau de Vie Framboise</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>20,2 %</t>
+        </is>
+      </c>
+      <c r="O47" s="10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="P47" s="10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>20,2 %</t>
+        </is>
+      </c>
+      <c r="R47" s="10" t="inlineStr">
+        <is>
+          <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Grand Marnier</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>352,9 %</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>19,1 %</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>19,1 %</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>eau_de_vie</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1 660,0 %</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>25,0 %</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>0,9 %</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>compatible</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Guignolet</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>liqueur</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="K50" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>non borne</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>25,0 %</t>
+        </is>
+      </c>
+      <c r="O50" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P50" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q50" s="10" t="inlineStr">
+        <is>
+          <t>25,0 %</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Les lignes ou le taux de la mesure publiee depasse le plafond de stock, et le plafonnement applique</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sur les lignes ci-dessous, le sur-versement calcule au taux de la source depasse l'ecart de bilan matiere de l'exercice. Il est ramene a l'ecart. La derniere colonne indique si, sur les trois exercices cumules, le bilan matiere de la meme boisson reste compatible : le depassement provient alors du decoupage annuel du stock (inventaire arrete au 31/03) et non d'une impossibilite materielle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Boisson</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Base versee a la main (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>dont verre (L)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>dont cocktails (L)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Taux des sources</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Plafond de stock</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement aux taux des sources (L)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Plafond (ecart, L)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement retenu apres plafonnement (L)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Retranche (L)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Achats factures 3 exercices (L)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Ecart 3 exercices (L)</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement 3 exercices (L)</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Compatible sur 3 exercices</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>85.72</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>85.72</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>10,6 %</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>516</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>82.78</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune rouge</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>17,3 %</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>36,9 %</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Picon</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>3,5 %</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>23,6 %</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>23,4 %</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Passoa</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>42,0 %</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>10,5 %</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Clan Campbell</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>31,1 %</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>10,2 %</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>20,0 %</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2,9 %</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>8 lignes plafonnees sur 101 lignes bornees par le stock ; total retranche : 18,56 L ; sur-versement retenu apres plafonnement : 475,36 L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Boissons sans achat facture connu sur les trois exercices (le bilan matiere ne les borne pas) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Cubis de vin (couleur non précisée)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Get 31</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Framboise</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Guignolet</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Variante prudente, ces boissons ramenees a zero : 439,77 L.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/public/documents/pieces-reponse-1/R1-sur-versement-fourchette.xlsx
+++ b/public/documents/pieces-reponse-1/R1-sur-versement-fourchette.xlsx
@@ -1461,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U231"/>
+  <dimension ref="A1:U234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15117,6 +15117,72 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL de la feuille : 171 lignes, 57 boissons</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr"/>
+      <c r="C233" s="6" t="inlineStr"/>
+      <c r="D233" s="7" t="n">
+        <v>6908</v>
+      </c>
+      <c r="E233" s="7" t="n">
+        <v>417.26</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>403.97</v>
+      </c>
+      <c r="G233" s="7" t="n">
+        <v>6921.29</v>
+      </c>
+      <c r="H233" s="7" t="n">
+        <v>566.3099999999999</v>
+      </c>
+      <c r="I233" s="7" t="n">
+        <v>6354.98</v>
+      </c>
+      <c r="J233" s="7" t="n">
+        <v>4319.37</v>
+      </c>
+      <c r="K233" s="7" t="n">
+        <v>1182.6</v>
+      </c>
+      <c r="L233" s="7" t="n">
+        <v>1431.54</v>
+      </c>
+      <c r="M233" s="7" t="n">
+        <v>960.1900000000001</v>
+      </c>
+      <c r="N233" s="7" t="n">
+        <v>516.72</v>
+      </c>
+      <c r="O233" s="7" t="n">
+        <v>1699.32</v>
+      </c>
+      <c r="P233" s="7" t="n">
+        <v>2035.61</v>
+      </c>
+      <c r="Q233" s="7" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="R233" s="7" t="inlineStr"/>
+      <c r="S233" s="7" t="inlineStr"/>
+      <c r="T233" s="7" t="n">
+        <v>493.92</v>
+      </c>
+      <c r="U233" s="7" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Ce total n'est pas celui que la reponse publie : il englobe 11 boissons jamais versees a la main (pichet ou bouteille seuls), auxquelles aucun taux de sur-versement ne s'applique. Le total du perimetre publie est celui de la feuille « Fourchette 3 exercices » : 5 534,4 L disponibles au service, 3 729,9 L vendus aux doses de la carte, soit 1 804,5 L d'ecart.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15128,7 +15194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -18474,6 +18540,79 @@
       <c r="R50" s="10" t="inlineStr">
         <is>
           <t>achats factures absents : non borne</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL : 46 boissons versees a la main</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr"/>
+      <c r="C51" s="7" t="n">
+        <v>5938.5</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>5534.38</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>3729.9</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>1182.6</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>1427.04</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>475.13</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>516.72</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>1804.48</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>1699.32</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>0,0 %</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>106,2 %</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>29,1 %</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>493.92</v>
+      </c>
+      <c r="P51" s="7" t="n">
+        <v>475.36</v>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>12,7 %</t>
+        </is>
+      </c>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
+          <t>perimetre publie dans la reponse</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Lecture du total : 1 804,5 L d'ecart pour 1 699,3 L verses a la main, soit une borne haute de 106,2 %. Le sur-versement retenu, 493,9 L, n'en couvre que 27,4 %, soit un rapport de 3,65 : les taux retenus n'absorbent pas l'ecart, ils en expliquent une part. Les 11 boissons servies uniquement au pichet ou a la bouteille sont hors de ce total : elles portent elles aussi un ecart de bilan matiere, mais aucun sur-versement ne leur est applique.</t>
         </is>
       </c>
     </row>
